--- a/config/PCS_125_英博.xlsx
+++ b/config/PCS_125_英博.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
+    <workbookView windowWidth="15404" windowHeight="11268" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -2752,40 +2752,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
